--- a/ONCToNandaMapping.xlsx
+++ b/ONCToNandaMapping.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T01:44:04+00:00</t>
+    <t>2026-01-03T21:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ONCToNandaMapping.xlsx
+++ b/ONCToNandaMapping.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T21:32:36+00:00</t>
+    <t>2026-01-26T10:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ONCToNandaMapping.xlsx
+++ b/ONCToNandaMapping.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T10:54:48+00:00</t>
+    <t>2026-01-26T11:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ONCToNandaMapping.xlsx
+++ b/ONCToNandaMapping.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T11:35:16+00:00</t>
+    <t>2026-01-26T23:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ONCToNandaMapping.xlsx
+++ b/ONCToNandaMapping.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T23:55:12+00:00</t>
+    <t>2026-01-27T00:24:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ONCToNandaMapping.xlsx
+++ b/ONCToNandaMapping.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.clinyq.ai/ConceptMap/onc-to-nanda</t>
+    <t>https://opennursingcoreig.com/ConceptMap/onc-to-nanda</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T00:24:44+00:00</t>
+    <t>2026-01-27T01:09:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t>https://fhir.clinyq.ai/ValueSet/onc-relational-findings-vs</t>
+    <t>https://opennursingcoreig.com/ValueSet/onc-relational-findings-vs</t>
   </si>
   <si>
     <t>Target</t>
@@ -102,7 +102,7 @@
     <t>Relationship</t>
   </si>
   <si>
-    <t>https://fhir.clinyq.ai/CodeSystem/onc-observation-codes</t>
+    <t>https://opennursingcoreig.com/CodeSystem/onc-observation-codes</t>
   </si>
   <si>
     <t>patient-story</t>

--- a/ONCToNandaMapping.xlsx
+++ b/ONCToNandaMapping.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T01:09:05+00:00</t>
+    <t>2026-01-27T08:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
